--- a/business_surveys/027_statement_ranking_survey--business_surveys.xlsx
+++ b/business_surveys/027_statement_ranking_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your favorite food</t>
+          <t>Select your favorite food</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Your favorite color</t>
+          <t>Select your favorite color</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>statement_4</t>
+          <t>statement_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How old are you</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Please enter your age</t>
-        </is>
-      </c>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -598,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Please select all that apply</t>
+          <t>Select your job title</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>statement_6</t>
+          <t>statement_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is your job</t>
+          <t>Select your height</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,24 +630,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>statement_7</t>
+          <t>statement_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How tall are you</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Please enter your height</t>
-        </is>
-      </c>
+          <t>Select your contact information</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -661,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>statement_8</t>
+          <t>statement_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Please select all that apply</t>
+          <t>Select your work time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -689,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>statement_9</t>
+          <t>statement_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Your contact info</t>
+          <t>Hours slept</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -707,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>statement_10</t>
+          <t>statement_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What time do you work</t>
+          <t>Select your phone number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>statement_11</t>
+          <t>statement_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How many hours do you sleep</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Please enter your sleep hours</t>
-        </is>
-      </c>
+          <t>Select your address</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -757,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>statement_12</t>
+          <t>statement_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is your phone number</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Please enter your phone number</t>
-        </is>
-      </c>
+          <t>Birthday</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -784,24 +768,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>statement_13</t>
+          <t>statement_15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Your statement</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Please enter your statement</t>
-        </is>
-      </c>
+          <t>Statement 15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -811,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>statement_14</t>
+          <t>statement_16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What time do you work</t>
+          <t>Statement 16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -839,19 +819,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>statement_15</t>
+          <t>statement_17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How many hours do you work</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Please enter the number of hours</t>
-        </is>
-      </c>
+          <t>Select your lunch time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -866,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>statement_16</t>
+          <t>statement_18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your address</t>
+          <t>Select your break time</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -884,217 +860,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>statement_17</t>
+          <t>statement_20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Your email</t>
+          <t>Select your finish work time</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>statement_18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What is your birthday</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>statement_19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is your favorite food</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>statement_20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is your job</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>statement_21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How many hours do you take for lunch</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Please enter your lunch hours</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>statement_22</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How many hours do you take for breaks</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Please enter your break hours</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>statement_23</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your address</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>statement_24</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What time do you go to work</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Please enter your work time</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>statement_25</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Your contact information</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1111,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1144,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
@@ -1161,29 +941,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Burger</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>statement_2_choices</t>
+          <t>statement_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
@@ -1195,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1212,216 +992,131 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>statement_5_choices</t>
+          <t>statement_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>statement_5_choices</t>
+          <t>statement_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>statement_5_choices</t>
+          <t>statement_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>statement_8_choices</t>
+          <t>statement_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>statement_8_choices</t>
+          <t>statement_15_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option E</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>statement_8_choices</t>
+          <t>statement_15_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_f</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option F</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>statement_19_choices</t>
+          <t>statement_15_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pizza</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>statement_19_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>burger</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Burger</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>statement_19_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>salad</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Salad</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>statement_25_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_g</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option G</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>statement_25_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_h</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option H</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>statement_25_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_i</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option I</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
